--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_nuble.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_nuble.xlsx
@@ -375,286 +375,286 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="C2">
-        <v>169456</v>
+        <v>96.27408215194475</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Ninhue</t>
         </is>
       </c>
       <c r="C3">
-        <v>53254</v>
+        <v>95.56853315012023</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="C4">
-        <v>30834</v>
+        <v>94.78986587183309</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="C5">
-        <v>27221</v>
+        <v>94.14752395244142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="C6">
-        <v>22165</v>
+        <v>93.62578193047747</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="C7">
-        <v>18982</v>
+        <v>93.43797276853253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="C8">
-        <v>16940</v>
+        <v>93.41387947546781</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coelemu</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="C9">
-        <v>16622</v>
+        <v>93.07915883056933</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="C10">
-        <v>15901</v>
+        <v>92.12741162760585</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="C11">
-        <v>14230</v>
+        <v>91.95517414052112</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="C12">
-        <v>12680</v>
+        <v>91.72179510101913</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="C13">
-        <v>12651</v>
+        <v>91.61546085232904</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="C14">
-        <v>11824</v>
+        <v>91.36943441636582</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Coelemu</t>
         </is>
       </c>
       <c r="C15">
-        <v>8156</v>
+        <v>91.32465249162134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="C16">
-        <v>5564</v>
+        <v>91.06409202958093</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="C17">
-        <v>5297</v>
+        <v>90.84446359327876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="C18">
-        <v>5130</v>
+        <v>90.58166862514689</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="C19">
-        <v>4941</v>
+        <v>89.05009725069652</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="C20">
-        <v>4622</v>
+        <v>84.44005939745468</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +710,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2022_nuble.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2022_nuble.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C647"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -655,6 +655,9411 @@
       </c>
       <c r="C20">
         <v>84.44005939745468</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>48.90072140158021</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>48.76331157677774</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>48.63685932388223</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>48.44931921331316</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>48.4053651266766</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>48.29360994536385</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>48.29312934919621</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>48.2511831928893</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>47.82672756740828</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>47.63722282806252</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>47.5924404272802</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>47.34641948382406</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>47.30913642052565</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>47.0672018645604</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>46.97720515361744</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>46.91245593419507</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>46.90716361771243</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>46.80522157334249</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>46.62815884476534</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>46.52276410785325</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>46.38450074515648</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>46.32287231246386</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>46.25335320417287</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>46.1719952128569</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>45.89634075955212</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>45.66232624581067</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>45.66232624581067</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>45.6029937911721</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>45.58715190805952</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>45.56943846043372</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>45.33217198511363</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>45.27502513284504</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>45.06020976304545</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>44.98865355521936</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>44.74127557160048</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>44.6382556987116</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>44.41265868049347</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>43.66921269095182</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>43.66204479132492</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>43.62182278881939</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>43.47165160230074</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>43.46069490938474</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>43.31324573066496</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>42.72722493823267</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>42.49643920756183</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>41.54608523290386</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>41.21388271499401</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>40.89039871267656</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>40.69795427196149</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>40.56354009077156</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>40.2556369381014</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>40.20131470829909</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>39.28355584857974</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>38.83706560628258</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>38.04078093700481</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>38.02765073857962</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>37.85252643948296</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>30.16270337922403</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>26.68852459016393</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>25.96630327056491</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>25.62988065419184</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>25.24876047187553</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>25.13284503805831</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>24.00945110868775</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>23.92648574373068</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>23.7908345838624</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>23.29241877256318</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>22.03101361573374</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>21.75152426953836</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>21.36480582943381</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>21.0620418380118</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>20.83476468567503</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>20.56457971928718</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>20.4524089306698</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>20.3198836786623</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>20.04108463434675</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>19.7077083676721</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>19.52639964837097</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>18.9110449307264</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>18.77836611195159</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>18.75853340110224</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>18.36232980332829</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>18.23443008225617</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>17.85800240673887</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>17.79238261144984</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>17.7601585728444</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>17.58011503697617</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>17.5619425173439</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>17.3789623087841</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>17.2876304023845</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>17.08532953515473</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>16.94648657890238</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>16.75261529394431</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>16.72737955346651</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>16.62546013955277</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>16.48005046522631</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>16.32229019969987</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>16.31074685443842</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>16.14318028767289</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>16.02300739523418</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>15.83746969871869</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>15.82829046898638</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>15.81214993537268</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>15.76154992548435</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>15.73567247422858</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>15.6696795398521</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>15.4835701828605</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>15.47075290997495</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>15.46710287168303</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>15.29020508353789</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>15.27903664379127</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>15.27316486161251</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>15.20264942438101</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>15.13838748495788</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>14.95532824032112</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>14.80718980125109</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>14.75826972010178</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>14.66849879766403</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>14.61104462301248</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>14.60908741277952</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>14.59473196400275</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>14.44125531936098</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>14.37598736176935</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>14.33102081268583</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>14.04230317273796</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>13.91356184798808</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>13.86614964814017</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>13.80968739264858</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>13.63459795416289</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>13.60164512338425</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>13.38937421020823</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>13.3769538349691</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>13.30234221348114</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>13.28432210634296</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>13.25380452656442</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>13.24157764995891</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>13.22867366962946</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>13.2267253657905</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>13.22569563723806</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>13.21892347096401</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>13.18515985638571</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>13.07890448404563</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>13.05202932236725</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>13.04700162074554</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>13.04601309534487</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>13.01163291684619</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>13.0097394884789</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>12.96222978858184</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>12.95481030687557</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>12.94009003809304</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>12.92399403874814</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>12.86757722791083</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>12.85840188014101</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>12.85689861514789</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>12.85538208709943</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>12.84077555816686</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>12.81125681449831</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>12.80698862699852</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>12.79534714649219</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>12.77911370663002</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>12.74051785572888</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>12.73646209386282</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>12.72440040212552</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>12.68627078548858</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>12.66745005875441</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>12.63463839972645</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>12.63444820981288</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>12.55673222390318</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>12.48989957289623</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>12.46217851739788</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>12.36868186323092</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>12.34381732012064</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>12.26533166458073</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>12.24250168355982</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>12.22947440742013</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>12.19076005961252</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>12.18064941486731</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>12.17748562037798</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>12.12286441294075</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>12.10589651022864</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>12.09942481511914</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>12.09437510685587</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>12.07727816720807</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>12.06505295007564</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>12.04195260908973</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>12.03576751117735</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>12.02493395265312</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>12.01177521947117</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>12.0054710206873</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>11.99384649195099</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>11.9836850964651</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>11.92427565508484</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>11.90909810753029</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>11.87003610108303</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>11.84880854560394</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>11.83304420964096</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>11.72697759125822</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>11.69675090252708</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>11.68587336527256</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>11.68585396625138</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>11.63987647478027</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>11.61546085232904</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>11.61225884455659</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>11.58983196897889</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>11.58833063209076</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>11.521344981045</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>11.48733233979136</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>11.43220647037441</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>11.41636846358075</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>11.3746869014292</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>11.34979719157672</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>11.34568433146632</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>11.32338724947927</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>11.32311772506262</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>11.27080181543116</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>11.23079132557806</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>11.21044162345789</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>11.17938553022795</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>11.15764139590854</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>11.13394229274947</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>11.05170387779083</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>11.00488984121752</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>10.91464783381969</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>10.9121540312876</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>10.83431257344301</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>10.81811024406773</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>10.80415782182757</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>10.79607415485278</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>10.73514256269323</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>10.72769533345253</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>10.67660208643815</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>10.60455896927651</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>10.5737042594944</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>10.55401082309325</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>10.52527254707631</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>10.51185159738921</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>10.45763993948563</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>10.39030402629417</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>10.38798498122653</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>10.36065573770492</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>10.28070802789201</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>10.22446512116911</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>10.12359142130135</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>10.1019131056678</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>9.77205153617443</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>9.672904081331959</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>9.515630367571282</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>7.112442832360826</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>6.307491454141378</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>5.569917743830787</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>5.203010823581122</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>5.149293760057215</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>5.015895795337898</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>4.911676001723395</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>4.616125150421179</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>4.568922349040802</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>4.383730484798686</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>4.247489880670767</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>3.895284655417127</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>3.755017480253787</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>3.705756591970861</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>3.616333725029377</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>3.48435630022226</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>3.429137760158573</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>3.326157801895536</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>3.290468986384266</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>3.109719246195264</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>3.082073184808958</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>3.021634185589129</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>2.893867585810714</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>2.864952951690059</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>2.816894390129658</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>2.801444043321299</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>2.718432297038456</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>2.655707699480255</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>2.625308134757601</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>2.369420276855921</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>2.278907160429885</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>2.226906249688562</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>2.187779433681073</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>2.17395058104398</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>2.145854778683981</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>2.136913767019667</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>2.127659574468085</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>2.093291577385858</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>2.07898786117285</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>2.076968272620447</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>2.053798618684115</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>2.017808415912681</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>1.95358401880141</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>1.927738658663281</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>1.920949561993602</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>1.913214649560548</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>1.847699345232756</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>1.820680178632772</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>1.81468110709988</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>1.758422350041085</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>1.755015397494544</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>1.744301288404361</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>1.705012325390304</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>1.684836471754212</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>1.642846618535435</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>1.559901813286879</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>1.5532035758065</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>1.507050528789659</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>1.476110319823903</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>1.461388845082269</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>1.455963958024284</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>1.448296122209166</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>1.439481347178726</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>1.430359377793671</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>1.424789410348977</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>1.419831467159183</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>1.417842807199275</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>1.40536843904941</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>1.399491094147583</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>1.377781297014807</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>1.357371363649954</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>1.350996162540083</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>1.329359165424739</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>1.324103071259821</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>1.287914629658834</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>1.253226497643037</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>1.249461439034899</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>1.242280626166882</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>1.210287443267776</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>1.197925978902199</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>1.196785775346213</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>1.185159738921333</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>1.176488175322151</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>1.169474727452924</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>1.154334526145677</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>1.153555219364599</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>1.128084606345476</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>1.11969720864217</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>1.114440414235399</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>1.108528517790095</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>1.07558567850302</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>1.051703877790834</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>1.037010548900411</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>1.023007395234182</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>1.017811704834606</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>1.009304526099984</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>0.9834624471182902</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>0.979054789080172</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>0.9765905500502657</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>0.9654925800107277</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>0.9531635168447001</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>0.9452285381328499</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>0.941066772572652</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>0.9338146811070999</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>0.9282451745984971</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>0.9264391479927152</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>0.926324859974149</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C376">
+        <v>0.9061102831594635</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C377">
+        <v>0.8888048411497731</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C378">
+        <v>0.8869610255082222</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C379">
+        <v>0.8808664259927798</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C380">
+        <v>0.8657508946092578</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C381">
+        <v>0.8621142827104032</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C382">
+        <v>0.8616125150421179</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C383">
+        <v>0.8584202682563339</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C384">
+        <v>0.8401551055579491</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C385">
+        <v>0.8398408722557831</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C386">
+        <v>0.8325074331020813</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C387">
+        <v>0.8258011503697618</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C388">
+        <v>0.8197048066094618</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C389">
+        <v>0.8131421350475249</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C390">
+        <v>0.7997466149338823</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C391">
+        <v>0.7990373044524669</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C392">
+        <v>0.7990373044524669</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C393">
+        <v>0.7925681625887107</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C394">
+        <v>0.7866976577865189</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C395">
+        <v>0.785671116971595</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C396">
+        <v>0.7796204479398188</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C397">
+        <v>0.7755581668625147</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C398">
+        <v>0.7753403933434191</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C399">
+        <v>0.763694302510851</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C400">
+        <v>0.7625235082920158</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C401">
+        <v>0.7557540364136036</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C402">
+        <v>0.75223691503682</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C403">
+        <v>0.7517216001682174</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C404">
+        <v>0.7509386733416771</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C405">
+        <v>0.7472116916652931</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C406">
+        <v>0.7387740967332332</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C407">
+        <v>0.7324429125376992</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C408">
+        <v>0.7220216606498195</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C409">
+        <v>0.7135777998017839</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C410">
+        <v>0.712158487634339</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C411">
+        <v>0.7021151586368978</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C412">
+        <v>0.6973001966744145</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C413">
+        <v>0.6925003683512597</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C414">
+        <v>0.6893580353295993</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C415">
+        <v>0.6821772224615826</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C416">
+        <v>0.680786686838124</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C417">
+        <v>0.6804581979825611</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C418">
+        <v>0.6778964667214462</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C419">
+        <v>0.6678155967255494</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C420">
+        <v>0.6579706799030359</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C421">
+        <v>0.6546329723225031</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C422">
+        <v>0.6544299207431837</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C423">
+        <v>0.6543075245365322</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C424">
+        <v>0.6532456861133936</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C425">
+        <v>0.6450287592440427</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C426">
+        <v>0.6409311919846766</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C427">
+        <v>0.638889368535562</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C428">
+        <v>0.6355204397114393</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C429">
+        <v>0.6345475910693302</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C430">
+        <v>0.6247307195174494</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C431">
+        <v>0.6208450085160157</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C432">
+        <v>0.6175499066494328</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C433">
+        <v>0.6144697720515362</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C434">
+        <v>0.6052316635322277</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C435">
+        <v>0.6020976304544866</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C436">
+        <v>0.593871248713279</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C437">
+        <v>0.5900232433398891</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C438">
+        <v>0.5767271597050748</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C439">
+        <v>0.5762009581768742</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C440">
+        <v>0.5721437511174683</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C441">
+        <v>0.5679903730445247</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C442">
+        <v>0.5631768953068592</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C443">
+        <v>0.5603576751117735</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C444">
+        <v>0.5463615488162167</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C445">
+        <v>0.535183349851338</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C446">
+        <v>0.5300051290818943</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C447">
+        <v>0.529500756429652</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C448">
+        <v>0.5265857411523337</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C449">
+        <v>0.5246690734055355</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C450">
+        <v>0.5245901639344263</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C451">
+        <v>0.5204226462703043</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C452">
+        <v>0.519745134943795</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C453">
+        <v>0.5170387779083431</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C454">
+        <v>0.516455139827482</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C455">
+        <v>0.5153617443012884</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C456">
+        <v>0.5094494658997535</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C457">
+        <v>0.5079071915040979</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C458">
+        <v>0.5049851094134403</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C459">
+        <v>0.5006257822277848</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C460">
+        <v>0.4992306377158489</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C461">
+        <v>0.4830152822868002</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C462">
+        <v>0.4757185332011893</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C463">
+        <v>0.4750969989706232</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C464">
+        <v>0.472972972972973</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C465">
+        <v>0.4725554343874955</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C466">
+        <v>0.4725015109059942</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C467">
+        <v>0.4683648315529992</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C468">
+        <v>0.4670975323149236</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C469">
+        <v>0.4649776453055142</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C470">
+        <v>0.4575829261133079</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C471">
+        <v>0.4558969276511398</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C472">
+        <v>0.4558969276511398</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C473">
+        <v>0.4543802253725918</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C474">
+        <v>0.4519309778142975</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C475">
+        <v>0.4467175967888126</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C476">
+        <v>0.4363139357619724</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C477">
+        <v>0.4299552777442025</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C478">
+        <v>0.4299552777442025</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C479">
+        <v>0.4294057025077293</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C480">
+        <v>0.4294057025077293</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C481">
+        <v>0.4164871463449663</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C482">
+        <v>0.4125534109326654</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C483">
+        <v>0.4117507324412067</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C484">
+        <v>0.4057810854212353</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C485">
+        <v>0.4000683877585912</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C486">
+        <v>0.397125567322239</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C487">
+        <v>0.397125567322239</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C488">
+        <v>0.397125567322239</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C489">
+        <v>0.3820870994248151</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C490">
+        <v>0.3819759160947818</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C491">
+        <v>0.3819759160947818</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C492">
+        <v>0.37821482602118</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C493">
+        <v>0.3754693366708385</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C494">
+        <v>0.3754512635379061</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C495">
+        <v>0.3721593158603215</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C496">
+        <v>0.359304084720121</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C497">
+        <v>0.3590357326038639</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C498">
+        <v>0.3578437031051599</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C499">
+        <v>0.356788899900892</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C500">
+        <v>0.356788899900892</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C501">
+        <v>0.3560792438171695</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C502">
+        <v>0.3536172093708561</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C503">
+        <v>0.3533278553820871</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C504">
+        <v>0.3463003578437031</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C505">
+        <v>0.3315161337851775</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C506">
+        <v>0.3296522169111587</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C507">
+        <v>0.3271537622682661</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C508">
+        <v>0.3263483339058743</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C509">
+        <v>0.3263483339058743</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C510">
+        <v>0.3248418533082578</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C511">
+        <v>0.3219076005961252</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C512">
+        <v>0.315946348733234</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C513">
+        <v>0.3116703220593328</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C514">
+        <v>0.3089785532533624</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C515">
+        <v>0.3089785532533624</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C516">
+        <v>0.3020480330042729</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C517">
+        <v>0.2919958777052559</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C518">
+        <v>0.2850581993823739</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C519">
+        <v>0.2786101035588498</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C520">
+        <v>0.2726281352235551</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C521">
+        <v>0.2654969410135057</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C522">
+        <v>0.265212907028142</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C523">
+        <v>0.2622950819672131</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C524">
+        <v>0.2585193889541715</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C525">
+        <v>0.2544529262086514</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C526">
+        <v>0.2533850661176657</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C527">
+        <v>0.2524925547067202</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C528">
+        <v>0.2504788566376897</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C529">
+        <v>0.245839636913767</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C530">
+        <v>0.2444113263785395</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C531">
+        <v>0.2431118314424635</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C532">
+        <v>0.2424102504905922</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C533">
+        <v>0.2232909653040192</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C534">
+        <v>0.2222602154214396</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C535">
+        <v>0.2181025081788441</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C536">
+        <v>0.2145539066690506</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C537">
+        <v>0.2077802147062218</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C538">
+        <v>0.1967213114754098</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C539">
+        <v>0.1962368694447651</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C540">
+        <v>0.1907600596125186</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C541">
+        <v>0.18910741301059</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C542">
+        <v>0.1889385091034009</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C543">
+        <v>0.1817520901490367</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C544">
+        <v>0.178394449950446</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C545">
+        <v>0.172876304023845</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C546">
+        <v>0.1717622810030917</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C547">
+        <v>0.1717622810030917</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C548">
+        <v>0.163576881134133</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C549">
+        <v>0.1547075290997495</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C550">
+        <v>0.1387512388503469</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C551">
+        <v>0.1374098248024734</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C552">
+        <v>0.1371087928464978</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C553">
+        <v>0.1320497104872385</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C554">
+        <v>0.1208724795340915</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C555">
+        <v>0.1187742497426558</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C556">
+        <v>0.109051254089422</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C557">
+        <v>0.103057368601855</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C558">
+        <v>0.094553706505295</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C559">
+        <v>0.08122302946950898</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C560">
+        <v>0.0780608052588332</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C561">
+        <v>0.07424930499197072</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C562">
+        <v>0.07359512169479052</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C563">
+        <v>0.07220216606498195</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C564">
+        <v>0.07180812868016659</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C565">
+        <v>0.07151796888968354</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C566">
+        <v>0.06496837066165156</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C567">
+        <v>0.06462731581214994</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C568">
+        <v>0.05946481665014866</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C569">
+        <v>0.05365126676602087</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C570">
+        <v>0.05256794406770751</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C571">
+        <v>0.04700352526439483</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C572">
+        <v>0.04662165662286533</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C573">
+        <v>0.04112808460634548</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C574">
+        <v>0.03697617091207888</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C575">
+        <v>0.03463003578437031</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C576">
+        <v>0.03435245620061834</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C577">
+        <v>0.03435245620061834</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C578">
+        <v>0.03369434416365824</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C579">
+        <v>0.03296522169111588</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C580">
+        <v>0.03237084034701541</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C581">
+        <v>0.02384500745156483</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C582">
+        <v>0.02154243860404998</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C583">
+        <v>0.01925391095066185</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C584">
+        <v>0.018910741301059</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C585">
+        <v>0.018910741301059</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C586">
+        <v>0.01817520901490367</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C587">
+        <v>0.01726728023069087</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C588">
+        <v>0.01717622810030917</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C589">
+        <v>0.01583656663235411</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C590">
+        <v>0.01473405039045234</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C591">
+        <v>0.01294833613880616</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C592">
+        <v>0.01175088131609871</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C593">
+        <v>0.01154334526145677</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C594">
+        <v>0.0105135888135415</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C595">
+        <v>0.01046431668012079</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C596">
+        <v>0.01025816378868183</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C597">
+        <v>0.007367025195226168</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C598">
+        <v>0.006838775859121217</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C599">
+        <v>0.004108463434675432</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>16101</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="C601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>16102</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="C603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>16103</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="C605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>El Carmen</t>
+        </is>
+      </c>
+      <c r="C608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>16105</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Pemuco</t>
+        </is>
+      </c>
+      <c r="C611">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C612">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Pinto</t>
+        </is>
+      </c>
+      <c r="C613">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C614">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>16107</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Quillón</t>
+        </is>
+      </c>
+      <c r="C615">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C616">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C617">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>16108</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>San Ignacio</t>
+        </is>
+      </c>
+      <c r="C618">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C619">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>16109</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Yungay</t>
+        </is>
+      </c>
+      <c r="C620">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C621">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C622">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>16201</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="C623">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C624">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C625">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>16202</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Cobquecura</t>
+        </is>
+      </c>
+      <c r="C626">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C627">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C628">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>16203</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Coelemu</t>
+        </is>
+      </c>
+      <c r="C629">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C630">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>16204</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Ninhue</t>
+        </is>
+      </c>
+      <c r="C631">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C632">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C633">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C634">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>16205</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Portezuelo</t>
+        </is>
+      </c>
+      <c r="C635">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C636">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>16207</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Treguaco</t>
+        </is>
+      </c>
+      <c r="C637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C638">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>16301</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="C639">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C640">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>16302</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Coihueco</t>
+        </is>
+      </c>
+      <c r="C641">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C642">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C643">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>16304</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>San Fabián</t>
+        </is>
+      </c>
+      <c r="C644">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C645">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C646">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>16305</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="C647">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
